--- a/moduli_aziende/aifecs/moduli_compilati/MOD-530-B-Ruoli_e_Requisiti.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-530-B-Ruoli_e_Requisiti.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0bc198ee17b840e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R77cb7be1a8ef47e8"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -345,9 +328,7 @@
       <x:c r="D2" s="4" t="str">
         <x:v>Approvazione del sistema nei limiti delle deleghe effettive.</x:v>
       </x:c>
-      <x:c r="E2" s="4" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E2" s="4"/>
     </x:row>
     <x:row r="3" ht="68" customHeight="1">
       <x:c r="A3" s="4" t="str">
@@ -362,9 +343,7 @@
       <x:c r="D3" s="4" t="str">
         <x:v>Richiedere evidenze e proporre azioni. Autorità da formalizzare.</x:v>
       </x:c>
-      <x:c r="E3" s="4" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E3" s="4"/>
     </x:row>
     <x:row r="4" ht="68" customHeight="1">
       <x:c r="A4" s="4" t="str">
@@ -377,11 +356,9 @@
         <x:v>Analisi fabbisogni, progettazione, riesame dei requisiti, coordinamento docenti e verifiche.</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
-        <x:v>Validazione didattica secondo delega da confermare.</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Validazione didattica secondo le deleghe attribuite.</x:v>
+      </x:c>
+      <x:c r="E4" s="4"/>
     </x:row>
     <x:row r="5" ht="68" customHeight="1">
       <x:c r="A5" s="4" t="str">
@@ -396,9 +373,7 @@
       <x:c r="D5" s="4" t="str">
         <x:v>Gestire documenti secondo procedura approvata.</x:v>
       </x:c>
-      <x:c r="E5" s="4" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E5" s="4"/>
     </x:row>
     <x:row r="6" ht="68" customHeight="1">
       <x:c r="A6" s="4" t="str">
@@ -413,9 +388,7 @@
       <x:c r="D6" s="4" t="str">
         <x:v>Istruttoria delle adesioni e segnalazione delle anomalie.</x:v>
       </x:c>
-      <x:c r="E6" s="4" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E6" s="4"/>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
       <x:c r="A7" s="4" t="str">
@@ -430,9 +403,7 @@
       <x:c r="D7" s="4" t="str">
         <x:v>Conduzione delle attività assegnate entro il programma approvato.</x:v>
       </x:c>
-      <x:c r="E7" s="4" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E7" s="4"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="4" t="str">
@@ -447,9 +418,7 @@
       <x:c r="D8" s="4" t="str">
         <x:v>Segnalazione anomalie e assistenza secondo istruzioni.</x:v>
       </x:c>
-      <x:c r="E8" s="4" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E8" s="4"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="4" t="str">
@@ -464,9 +433,7 @@
       <x:c r="D9" s="4" t="str">
         <x:v>Responsabilità locale da definire nell’accordo con AIFECS.</x:v>
       </x:c>
-      <x:c r="E9" s="4" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E9" s="4"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="4" t="str">
@@ -481,9 +448,7 @@
       <x:c r="D10" s="4" t="str">
         <x:v>Operare sui sistemi secondo profili e incarichi approvati.</x:v>
       </x:c>
-      <x:c r="E10" s="4" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E10" s="4"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="4" t="str">
@@ -498,9 +463,7 @@
       <x:c r="D11" s="4" t="str">
         <x:v>Operare entro limiti di spesa e deleghe confermate.</x:v>
       </x:c>
-      <x:c r="E11" s="4" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E11" s="4"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12"/>
@@ -564,6 +527,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8470544eeb44f84"/>
 </x:worksheet>
 </file>